--- a/Schibsted modell.xlsx
+++ b/Schibsted modell.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E41C3D8-DFE6-934F-8E28-48A4DE5B255A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4817DE1-B841-744F-A9CA-E18BE4359C1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25340" yWindow="500" windowWidth="25500" windowHeight="26500" xr2:uid="{CF2EC152-6970-7944-95E4-562C87096A91}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" activeTab="5" xr2:uid="{CF2EC152-6970-7944-95E4-562C87096A91}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Modell" sheetId="2" r:id="rId2"/>
     <sheet name="SOTP" sheetId="5" r:id="rId3"/>
     <sheet name="Segmenter" sheetId="4" r:id="rId4"/>
-    <sheet name="Nøkkeltall" sheetId="3" r:id="rId5"/>
-    <sheet name="Nedsideberegning" sheetId="6" r:id="rId6"/>
+    <sheet name="ARPA" sheetId="7" r:id="rId5"/>
+    <sheet name="NAA" sheetId="8" r:id="rId6"/>
+    <sheet name="Recommerce" sheetId="9" r:id="rId7"/>
+    <sheet name="Nøkkeltall" sheetId="3" r:id="rId8"/>
+    <sheet name="Nedsideberegning" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">SOTP!$A$60:$A$79</definedName>
@@ -106,8 +109,98 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2EDCE919-97FE-3C4A-9ED1-492F491396BC}</author>
+    <author>tc={5721A1CA-DAD0-6D4C-931E-50DA55EB8D05}</author>
+    <author>august hodt</author>
+  </authors>
+  <commentList>
+    <comment ref="AA4" authorId="0" shapeId="0" xr:uid="{2EDCE919-97FE-3C4A-9ED1-492F491396BC}">
+      <text>
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    januar-februar</t>
+      </text>
+    </comment>
+    <comment ref="AB4" authorId="1" shapeId="0" xr:uid="{5721A1CA-DAD0-6D4C-931E-50DA55EB8D05}">
+      <text>
+        <t xml:space="preserve">[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    April-mai
+</t>
+      </text>
+    </comment>
+    <comment ref="U22" authorId="2" shapeId="0" xr:uid="{2E231A30-FD59-F54E-9238-4034B6230763}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>august hodt:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Månedlig gjennomsnitt antall eiendomskontorer (ikke annonser)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={BD81F970-C185-BF49-9356-556DCEF192C8}</author>
+    <author>tc={8167A84A-6715-914C-9F78-89DA8FC5973F}</author>
+  </authors>
+  <commentList>
+    <comment ref="Z5" authorId="0" shapeId="0" xr:uid="{BD81F970-C185-BF49-9356-556DCEF192C8}">
+      <text>
+        <t>[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    januar-februar</t>
+      </text>
+    </comment>
+    <comment ref="AA5" authorId="1" shapeId="0" xr:uid="{8167A84A-6715-914C-9F78-89DA8FC5973F}">
+      <text>
+        <t xml:space="preserve">[Kommentartråd]
+Din versjon av Excel lar deg lese denne kommentartråden. Eventuelle endringer i den vil imidlertid bli fjernet hvis filen åpnes i en nyere versjon av Excel. Finn ut mer: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
+    April-mai
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="343">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -1159,12 +1252,90 @@
   <si>
     <t>26.05.26: Vend kjøper tilbake 725 000 aksjer</t>
   </si>
+  <si>
+    <t>01.06.26: Vend kjøper tilbake 500 000 aksjer</t>
+  </si>
+  <si>
+    <t>08.06.26: Styreleder kjøper 4 000 aksjer</t>
+  </si>
+  <si>
+    <t>08.06.26: Vend kjøper tilbake 644 000 aksjer</t>
+  </si>
+  <si>
+    <t>08.06.26: Polaris media selger seg helt ut av Vend med et salg av 3 218 304 aksjer til 239</t>
+  </si>
+  <si>
+    <t>15.06.26: Vend kjøper tilbake 667 000 aksjer</t>
+  </si>
+  <si>
+    <t>Vertical</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Professional</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Residential for sale</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>Tallene er i tusen</t>
+  </si>
+  <si>
+    <t>QTD</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Take rate</t>
+  </si>
+  <si>
+    <t>GMV = Gross merchandise value</t>
+  </si>
+  <si>
+    <t>Transacted GMV (million)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="11">
     <numFmt numFmtId="8" formatCode="&quot;kr&quot;\ #,##0.00_);[Red]\(&quot;kr&quot;\ #,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
@@ -1172,8 +1343,12 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="#,##0.000"/>
+    <numFmt numFmtId="170" formatCode="&quot;kr&quot;\ #,##0"/>
+    <numFmt numFmtId="171" formatCode="[$SEK]\ #,##0"/>
+    <numFmt numFmtId="172" formatCode="[$DKK]\ #,##0"/>
+    <numFmt numFmtId="173" formatCode="[$EUR]\ #,##0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1290,6 +1465,15 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1602,7 +1786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1727,9 +1911,44 @@
     <xf numFmtId="167" fontId="14" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="15" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="14" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperkobling" xfId="1" builtinId="8"/>
@@ -2433,8 +2652,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>23044</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>772344</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
@@ -2912,6 +3131,30 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="AA4" dT="2026-06-16T09:48:34.02" personId="{2D39DD3A-A459-8948-B7BD-8142FDC1AAEC}" id="{2EDCE919-97FE-3C4A-9ED1-492F491396BC}">
+    <text>januar-februar</text>
+  </threadedComment>
+  <threadedComment ref="AB4" dT="2026-06-16T09:45:54.53" personId="{2D39DD3A-A459-8948-B7BD-8142FDC1AAEC}" id="{5721A1CA-DAD0-6D4C-931E-50DA55EB8D05}">
+    <text xml:space="preserve">April-mai
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="Z5" dT="2026-06-16T09:48:34.02" personId="{2D39DD3A-A459-8948-B7BD-8142FDC1AAEC}" id="{BD81F970-C185-BF49-9356-556DCEF192C8}">
+    <text>januar-februar</text>
+  </threadedComment>
+  <threadedComment ref="AA5" dT="2026-06-16T09:45:54.53" personId="{2D39DD3A-A459-8948-B7BD-8142FDC1AAEC}" id="{8167A84A-6715-914C-9F78-89DA8FC5973F}">
+    <text xml:space="preserve">April-mai
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
   <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
@@ -2937,20 +3180,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17698142-E94C-684E-8A27-765BEE6464F1}">
-  <dimension ref="A1:AA66"/>
+  <dimension ref="A1:AA71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="13" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="10.83203125" style="1"/>
     <col min="14" max="14" width="12.6640625" style="1" customWidth="1"/>
     <col min="15" max="15" width="10.83203125" style="1"/>
     <col min="16" max="16" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="20" width="10.83203125" style="1"/>
-    <col min="21" max="21" width="13" style="76" customWidth="1"/>
-    <col min="22" max="22" width="16.5" style="1" customWidth="1"/>
-    <col min="23" max="23" width="26.1640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13" style="102" customWidth="1"/>
+    <col min="22" max="22" width="16.5" style="14" customWidth="1"/>
+    <col min="23" max="23" width="26.1640625" style="14" customWidth="1"/>
     <col min="24" max="24" width="17.6640625" style="14" customWidth="1"/>
-    <col min="25" max="25" width="19.5" style="1" customWidth="1"/>
+    <col min="25" max="25" width="19.5" style="14" customWidth="1"/>
     <col min="26" max="26" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="16384" width="10.83203125" style="1"/>
   </cols>
@@ -2960,32 +3204,47 @@
         <v>135</v>
       </c>
       <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
       <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H2" s="1" t="s">
         <v>173</v>
       </c>
       <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
       <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H3" s="1" t="s">
         <v>136</v>
       </c>
       <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
       <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H4" s="1" t="s">
         <v>137</v>
       </c>
       <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
       <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
       <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H6" s="2" t="s">
@@ -2997,7 +3256,10 @@
       <c r="U6" s="2" t="s">
         <v>289</v>
       </c>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
       <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="H7" s="1" t="s">
@@ -3171,7 +3433,7 @@
       </c>
       <c r="W14" s="14">
         <f>SUM(V8:V149)</f>
-        <v>9616983</v>
+        <v>11470983</v>
       </c>
       <c r="X14" s="14">
         <f>532167563-Y13</f>
@@ -3529,8 +3791,8 @@
       <c r="Z26" s="14"/>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>316</v>
+      <c r="A27" s="76" t="s">
+        <v>321</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -3542,9 +3804,9 @@
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="U28" s="76">
+        <v>320</v>
+      </c>
+      <c r="U28" s="102">
         <v>46153</v>
       </c>
       <c r="V28" s="14">
@@ -3564,9 +3826,9 @@
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="U29" s="76">
+        <v>319</v>
+      </c>
+      <c r="U29" s="102">
         <v>46160</v>
       </c>
       <c r="V29" s="14">
@@ -3587,9 +3849,9 @@
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="U30" s="76">
+        <v>318</v>
+      </c>
+      <c r="U30" s="102">
         <v>46168</v>
       </c>
       <c r="V30" s="14">
@@ -3609,76 +3871,127 @@
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>297</v>
+        <v>317</v>
+      </c>
+      <c r="U31" s="102">
+        <v>46174</v>
+      </c>
+      <c r="V31" s="14">
+        <v>500000</v>
+      </c>
+      <c r="W31" s="14">
+        <f>SUM(V28:V31)</f>
+        <v>2614000</v>
+      </c>
+      <c r="X31" s="14">
+        <v>120735826</v>
+      </c>
+      <c r="Y31" s="14">
+        <f>SUM(X28:X31)</f>
+        <v>639653140</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>296</v>
+        <v>316</v>
+      </c>
+      <c r="U32" s="102">
+        <v>46181</v>
+      </c>
+      <c r="V32" s="14">
+        <v>677000</v>
+      </c>
+      <c r="W32" s="14">
+        <f>SUM(V28:V32)</f>
+        <v>3291000</v>
+      </c>
+      <c r="X32" s="14">
+        <v>160627648</v>
+      </c>
+      <c r="Y32" s="14">
+        <f>SUM(X28:X32)</f>
+        <v>800280788</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>295</v>
+        <v>315</v>
+      </c>
+      <c r="U33" s="102">
+        <v>46188</v>
+      </c>
+      <c r="V33" s="14">
+        <v>677000</v>
+      </c>
+      <c r="W33" s="14">
+        <f>SUM(V28:V33)</f>
+        <v>3968000</v>
+      </c>
+      <c r="X33" s="14">
+        <v>163700945</v>
+      </c>
+      <c r="Y33" s="14">
+        <f>SUM(X28:X33)</f>
+        <v>963981733</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="V40" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="V40" s="15"/>
       <c r="AA40" s="79"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="V41" s="2"/>
+      <c r="V41" s="15"/>
       <c r="AA41" s="78"/>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="V42" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="V42" s="15"/>
       <c r="AA42" s="79"/>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>310</v>
@@ -3686,7 +3999,7 @@
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>312</v>
@@ -3694,111 +4007,136 @@
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>237</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>247</v>
       </c>
     </row>
@@ -3953,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>52</v>
@@ -4132,7 +4470,7 @@
       </c>
       <c r="B6" s="6">
         <f>B4*B5</f>
-        <v>54315</v>
+        <v>51120</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>54</v>
@@ -4417,7 +4755,7 @@
       </c>
       <c r="B9" s="7">
         <f>B6-B7+B8</f>
-        <v>50939</v>
+        <v>47744</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>59</v>
@@ -4746,7 +5084,7 @@
       </c>
       <c r="B12" s="40">
         <f>B4/(T65/B5)</f>
-        <v>3.0391114592658908</v>
+        <v>2.8603401969561326</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>34</v>
@@ -8492,7 +8830,7 @@
       </c>
       <c r="AS38" s="41">
         <f>(AS37-B4)/B4</f>
-        <v>0.17940003167456053</v>
+        <v>0.25311253365422054</v>
       </c>
     </row>
     <row r="39" spans="2:45" x14ac:dyDescent="0.25">
@@ -15074,11 +15412,11 @@
       <c r="B8" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="102" t="s">
+      <c r="C8" s="103" t="s">
         <v>200</v>
       </c>
       <c r="D8" s="54">
-        <f t="shared" ref="D8:D12" si="0">(E8*1000)/$E$30</f>
+        <f>(E8*1000)/$E$30</f>
         <v>194.27675988428157</v>
       </c>
       <c r="E8" s="55">
@@ -15103,9 +15441,9 @@
       <c r="B9" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="102"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="54">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D8:D12" si="0">(E9*1000)/$E$30</f>
         <v>99.180327868852459</v>
       </c>
       <c r="E9" s="55">
@@ -15130,7 +15468,7 @@
       <c r="B10" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="54">
         <f t="shared" si="0"/>
         <v>54.387656702025076</v>
@@ -15157,7 +15495,7 @@
       <c r="B11" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="102"/>
+      <c r="C11" s="103"/>
       <c r="D11" s="54">
         <f>(E11*1000)/$E$30</f>
         <v>14.946962391513983</v>
@@ -15183,7 +15521,7 @@
       <c r="B12" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="103"/>
       <c r="D12" s="54">
         <f t="shared" si="0"/>
         <v>-13.741562198649952</v>
@@ -19904,6 +20242,2190 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1322B806-2B16-F241-9CD3-A5DEE32230A2}">
+  <dimension ref="B4:X26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="20.33203125" style="1" customWidth="1"/>
+    <col min="5" max="15" width="10.83203125" style="1"/>
+    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="V4" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="W4" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="X4" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" s="105" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="104" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="105" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="105" t="s">
+        <v>326</v>
+      </c>
+      <c r="M5" s="105">
+        <v>438</v>
+      </c>
+      <c r="N5" s="105">
+        <v>439</v>
+      </c>
+      <c r="O5" s="105">
+        <v>428</v>
+      </c>
+      <c r="P5" s="105">
+        <v>434</v>
+      </c>
+      <c r="Q5" s="105">
+        <v>461</v>
+      </c>
+      <c r="R5" s="105">
+        <v>497</v>
+      </c>
+      <c r="S5" s="105">
+        <v>518</v>
+      </c>
+      <c r="T5" s="105">
+        <v>540</v>
+      </c>
+      <c r="U5" s="105">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" s="112" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="111"/>
+      <c r="D6" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q6" s="112">
+        <f t="shared" ref="I6:T6" si="0">(Q5-M5)/M5</f>
+        <v>5.2511415525114152E-2</v>
+      </c>
+      <c r="R6" s="112">
+        <f t="shared" si="0"/>
+        <v>0.13211845102505695</v>
+      </c>
+      <c r="S6" s="112">
+        <f t="shared" si="0"/>
+        <v>0.2102803738317757</v>
+      </c>
+      <c r="T6" s="112">
+        <f t="shared" si="0"/>
+        <v>0.24423963133640553</v>
+      </c>
+      <c r="U6" s="112">
+        <f>(U5-Q5)/Q5</f>
+        <v>0.27114967462039047</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" s="105" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="105" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" s="105" t="s">
+        <v>328</v>
+      </c>
+      <c r="M7" s="105">
+        <v>622</v>
+      </c>
+      <c r="N7" s="105">
+        <v>596</v>
+      </c>
+      <c r="O7" s="105">
+        <v>653</v>
+      </c>
+      <c r="P7" s="105">
+        <v>698</v>
+      </c>
+      <c r="Q7" s="105">
+        <v>704</v>
+      </c>
+      <c r="R7" s="105">
+        <v>715</v>
+      </c>
+      <c r="S7" s="105">
+        <v>734</v>
+      </c>
+      <c r="T7" s="105">
+        <v>766</v>
+      </c>
+      <c r="U7" s="105">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D8" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="112"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="112">
+        <f t="shared" ref="I8:T8" si="1">(Q7-M7)/M7</f>
+        <v>0.13183279742765272</v>
+      </c>
+      <c r="R8" s="112">
+        <f t="shared" si="1"/>
+        <v>0.19966442953020133</v>
+      </c>
+      <c r="S8" s="112">
+        <f t="shared" si="1"/>
+        <v>0.12404287901990811</v>
+      </c>
+      <c r="T8" s="112">
+        <f t="shared" si="1"/>
+        <v>9.7421203438395415E-2</v>
+      </c>
+      <c r="U8" s="112">
+        <f>(U7-Q7)/Q7</f>
+        <v>0.12642045454545456</v>
+      </c>
+      <c r="V8" s="112"/>
+      <c r="W8" s="112"/>
+      <c r="X8" s="112"/>
+    </row>
+    <row r="9" spans="2:24" s="106" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="D9" s="106" t="s">
+        <v>326</v>
+      </c>
+      <c r="M9" s="106">
+        <v>309</v>
+      </c>
+      <c r="N9" s="106">
+        <v>309</v>
+      </c>
+      <c r="O9" s="106">
+        <v>585</v>
+      </c>
+      <c r="P9" s="106">
+        <v>624</v>
+      </c>
+      <c r="Q9" s="106">
+        <v>718</v>
+      </c>
+      <c r="R9" s="106">
+        <v>720</v>
+      </c>
+      <c r="S9" s="106">
+        <v>702</v>
+      </c>
+      <c r="T9" s="106">
+        <v>720</v>
+      </c>
+      <c r="U9" s="106">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D10" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="112">
+        <f t="shared" ref="I10:T10" si="2">(Q9-M9)/M9</f>
+        <v>1.3236245954692556</v>
+      </c>
+      <c r="R10" s="112">
+        <f t="shared" si="2"/>
+        <v>1.3300970873786409</v>
+      </c>
+      <c r="S10" s="112">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="T10" s="112">
+        <f t="shared" si="2"/>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="U10" s="112">
+        <f>(U9-Q9)/Q9</f>
+        <v>-4.178272980501393E-3</v>
+      </c>
+      <c r="V10" s="112"/>
+      <c r="W10" s="112"/>
+      <c r="X10" s="112"/>
+    </row>
+    <row r="11" spans="2:24" s="106" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="D11" s="106" t="s">
+        <v>328</v>
+      </c>
+      <c r="M11" s="106">
+        <v>171</v>
+      </c>
+      <c r="N11" s="106">
+        <v>177</v>
+      </c>
+      <c r="O11" s="106">
+        <v>194</v>
+      </c>
+      <c r="P11" s="106">
+        <v>234</v>
+      </c>
+      <c r="Q11" s="106">
+        <v>246</v>
+      </c>
+      <c r="R11" s="106">
+        <v>304</v>
+      </c>
+      <c r="S11" s="106">
+        <v>301</v>
+      </c>
+      <c r="T11" s="106">
+        <v>298</v>
+      </c>
+      <c r="U11" s="106">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D12" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="112">
+        <f t="shared" ref="I12:T12" si="3">(Q11-M11)/M11</f>
+        <v>0.43859649122807015</v>
+      </c>
+      <c r="R12" s="112">
+        <f t="shared" si="3"/>
+        <v>0.71751412429378536</v>
+      </c>
+      <c r="S12" s="112">
+        <f t="shared" si="3"/>
+        <v>0.55154639175257736</v>
+      </c>
+      <c r="T12" s="112">
+        <f t="shared" si="3"/>
+        <v>0.27350427350427353</v>
+      </c>
+      <c r="U12" s="112">
+        <f>(U11-Q11)/Q11</f>
+        <v>8.5365853658536592E-2</v>
+      </c>
+      <c r="V12" s="112"/>
+      <c r="W12" s="112"/>
+      <c r="X12" s="112"/>
+    </row>
+    <row r="13" spans="2:24" s="107" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="107" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="107" t="s">
+        <v>326</v>
+      </c>
+      <c r="M13" s="107">
+        <v>4645</v>
+      </c>
+      <c r="N13" s="107">
+        <v>4585</v>
+      </c>
+      <c r="O13" s="107">
+        <v>313</v>
+      </c>
+      <c r="P13" s="107">
+        <v>316</v>
+      </c>
+      <c r="Q13" s="107">
+        <v>341</v>
+      </c>
+      <c r="R13" s="107">
+        <v>349</v>
+      </c>
+      <c r="S13" s="107">
+        <v>375</v>
+      </c>
+      <c r="T13" s="107">
+        <v>382</v>
+      </c>
+      <c r="U13" s="107">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D14" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="112">
+        <f t="shared" ref="I14:T14" si="4">(Q13-M13)/M13</f>
+        <v>-0.92658772874058126</v>
+      </c>
+      <c r="R14" s="112">
+        <f t="shared" si="4"/>
+        <v>-0.92388222464558345</v>
+      </c>
+      <c r="S14" s="112">
+        <f t="shared" si="4"/>
+        <v>0.19808306709265175</v>
+      </c>
+      <c r="T14" s="112">
+        <f t="shared" si="4"/>
+        <v>0.20886075949367089</v>
+      </c>
+      <c r="U14" s="112">
+        <f>(U13-Q13)/Q13</f>
+        <v>0.88856304985337242</v>
+      </c>
+      <c r="V14" s="112"/>
+      <c r="W14" s="112"/>
+      <c r="X14" s="112"/>
+    </row>
+    <row r="15" spans="2:24" s="107" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="107" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" s="107" t="s">
+        <v>328</v>
+      </c>
+      <c r="M15" s="107">
+        <v>146</v>
+      </c>
+      <c r="N15" s="107">
+        <v>161</v>
+      </c>
+      <c r="O15" s="107">
+        <v>168</v>
+      </c>
+      <c r="P15" s="107">
+        <v>167</v>
+      </c>
+      <c r="Q15" s="107">
+        <v>179</v>
+      </c>
+      <c r="R15" s="107">
+        <v>266</v>
+      </c>
+      <c r="S15" s="107">
+        <v>262</v>
+      </c>
+      <c r="T15" s="107">
+        <v>198</v>
+      </c>
+      <c r="U15" s="107">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D16" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="112">
+        <f t="shared" ref="I16:T16" si="5">(Q15-M15)/M15</f>
+        <v>0.22602739726027396</v>
+      </c>
+      <c r="R16" s="112">
+        <f t="shared" si="5"/>
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="S16" s="112">
+        <f t="shared" si="5"/>
+        <v>0.55952380952380953</v>
+      </c>
+      <c r="T16" s="112">
+        <f t="shared" si="5"/>
+        <v>0.18562874251497005</v>
+      </c>
+      <c r="U16" s="112">
+        <f>(U15-Q15)/Q15</f>
+        <v>-0.12290502793296089</v>
+      </c>
+      <c r="V16" s="112"/>
+      <c r="W16" s="112"/>
+      <c r="X16" s="112"/>
+    </row>
+    <row r="17" spans="2:21" s="77" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="2:21" s="105" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="104" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" s="105" t="s">
+        <v>325</v>
+      </c>
+      <c r="D18" s="105" t="s">
+        <v>331</v>
+      </c>
+      <c r="M18" s="105">
+        <v>2925</v>
+      </c>
+      <c r="N18" s="105">
+        <v>3200</v>
+      </c>
+      <c r="O18" s="105">
+        <v>3026</v>
+      </c>
+      <c r="P18" s="105">
+        <v>3153</v>
+      </c>
+      <c r="Q18" s="105">
+        <v>3148</v>
+      </c>
+      <c r="R18" s="105">
+        <v>3511</v>
+      </c>
+      <c r="S18" s="105">
+        <v>3454</v>
+      </c>
+      <c r="T18" s="105">
+        <v>3718</v>
+      </c>
+      <c r="U18" s="105">
+        <v>3782</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="114"/>
+      <c r="D19" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="112">
+        <f t="shared" ref="I19:T19" si="6">(Q18-M18)/M18</f>
+        <v>7.6239316239316235E-2</v>
+      </c>
+      <c r="R19" s="112">
+        <f t="shared" si="6"/>
+        <v>9.7187499999999996E-2</v>
+      </c>
+      <c r="S19" s="112">
+        <f t="shared" si="6"/>
+        <v>0.14144084600132187</v>
+      </c>
+      <c r="T19" s="112">
+        <f t="shared" si="6"/>
+        <v>0.17919441801458927</v>
+      </c>
+      <c r="U19" s="112">
+        <f>(U18-Q18)/Q18</f>
+        <v>0.2013977128335451</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" s="105" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="105" t="s">
+        <v>325</v>
+      </c>
+      <c r="D20" s="105" t="s">
+        <v>332</v>
+      </c>
+      <c r="M20" s="105">
+        <v>4645</v>
+      </c>
+      <c r="N20" s="105">
+        <v>4585</v>
+      </c>
+      <c r="O20" s="105">
+        <v>4385</v>
+      </c>
+      <c r="P20" s="105">
+        <v>4361</v>
+      </c>
+      <c r="Q20" s="105">
+        <v>4943</v>
+      </c>
+      <c r="R20" s="105">
+        <v>4912</v>
+      </c>
+      <c r="S20" s="105">
+        <v>5153</v>
+      </c>
+      <c r="T20" s="105">
+        <v>5262</v>
+      </c>
+      <c r="U20" s="105">
+        <v>5866</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112">
+        <f t="shared" ref="I21:T21" si="7">(Q20-M20)/M20</f>
+        <v>6.4155005382131328E-2</v>
+      </c>
+      <c r="R21" s="112">
+        <f t="shared" si="7"/>
+        <v>7.131952017448201E-2</v>
+      </c>
+      <c r="S21" s="112">
+        <f t="shared" si="7"/>
+        <v>0.17514253135689853</v>
+      </c>
+      <c r="T21" s="112">
+        <f t="shared" si="7"/>
+        <v>0.20660398991057097</v>
+      </c>
+      <c r="U21" s="112">
+        <f>(U20-Q20)/Q20</f>
+        <v>0.18672870726279586</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" s="108" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="108" t="s">
+        <v>333</v>
+      </c>
+      <c r="D22" s="108" t="s">
+        <v>331</v>
+      </c>
+      <c r="M22" s="108">
+        <v>19</v>
+      </c>
+      <c r="N22" s="108">
+        <v>19</v>
+      </c>
+      <c r="O22" s="108">
+        <v>20</v>
+      </c>
+      <c r="P22" s="108">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="108">
+        <v>21</v>
+      </c>
+      <c r="R22" s="108">
+        <v>22</v>
+      </c>
+      <c r="S22" s="108">
+        <v>24</v>
+      </c>
+      <c r="T22" s="108">
+        <v>26</v>
+      </c>
+      <c r="U22" s="108">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="112">
+        <f t="shared" ref="I23:T23" si="8">(Q22-M22)/M22</f>
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="R23" s="112">
+        <f t="shared" si="8"/>
+        <v>0.15789473684210525</v>
+      </c>
+      <c r="S23" s="112">
+        <f t="shared" si="8"/>
+        <v>0.2</v>
+      </c>
+      <c r="T23" s="112">
+        <f t="shared" si="8"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="U23" s="112">
+        <f>(U22-Q22)/Q22</f>
+        <v>19.476190476190474</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" s="77" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:21" s="105" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="104" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>325</v>
+      </c>
+      <c r="D25" s="105" t="s">
+        <v>331</v>
+      </c>
+      <c r="M25" s="105">
+        <v>6685</v>
+      </c>
+      <c r="N25" s="105">
+        <v>6763</v>
+      </c>
+      <c r="O25" s="105">
+        <v>6967</v>
+      </c>
+      <c r="P25" s="105">
+        <v>7303</v>
+      </c>
+      <c r="Q25" s="105">
+        <v>7891</v>
+      </c>
+      <c r="R25" s="105">
+        <v>8229</v>
+      </c>
+      <c r="S25" s="105">
+        <v>8185</v>
+      </c>
+      <c r="T25" s="105">
+        <v>8856</v>
+      </c>
+      <c r="U25" s="105">
+        <v>8899</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="112">
+        <f t="shared" ref="I26:T26" si="9">(Q25-M25)/M25</f>
+        <v>0.18040388930441287</v>
+      </c>
+      <c r="R26" s="112">
+        <f t="shared" si="9"/>
+        <v>0.2167677066390655</v>
+      </c>
+      <c r="S26" s="112">
+        <f t="shared" si="9"/>
+        <v>0.17482417109229223</v>
+      </c>
+      <c r="T26" s="112">
+        <f t="shared" si="9"/>
+        <v>0.21265233465699027</v>
+      </c>
+      <c r="U26" s="112">
+        <f>(U25-Q25)/Q25</f>
+        <v>0.12774046381954124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CC1CFB6-9DE7-1D42-827C-C8B6E5DDB66A}">
+  <dimension ref="B2:AD26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="13.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="20.33203125" style="1" customWidth="1"/>
+    <col min="5" max="15" width="10.83203125" style="1"/>
+    <col min="16" max="16" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="10.83203125" style="1"/>
+    <col min="26" max="26" width="10.83203125" style="4"/>
+    <col min="27" max="16384" width="10.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="3" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="AA3" s="120" t="s">
+        <v>335</v>
+      </c>
+      <c r="AB3" s="120"/>
+    </row>
+    <row r="4" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="V4" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="W4" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="X4" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA4" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="AB4" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="AC4" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD4" s="13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="2:30" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="109" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="110" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="110" t="s">
+        <v>326</v>
+      </c>
+      <c r="M5" s="110">
+        <v>149</v>
+      </c>
+      <c r="N5" s="110">
+        <v>156</v>
+      </c>
+      <c r="O5" s="110">
+        <v>158</v>
+      </c>
+      <c r="P5" s="110">
+        <v>162</v>
+      </c>
+      <c r="Q5" s="110">
+        <v>156</v>
+      </c>
+      <c r="R5" s="110">
+        <v>152</v>
+      </c>
+      <c r="S5" s="110">
+        <v>148</v>
+      </c>
+      <c r="T5" s="110">
+        <v>154</v>
+      </c>
+      <c r="U5" s="110">
+        <v>159</v>
+      </c>
+      <c r="Z5" s="115"/>
+    </row>
+    <row r="6" spans="2:30" s="112" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B6" s="111"/>
+      <c r="D6" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q6" s="112">
+        <f t="shared" ref="Q6:T6" si="0">(Q5-M5)/M5</f>
+        <v>4.6979865771812082E-2</v>
+      </c>
+      <c r="R6" s="112">
+        <f t="shared" si="0"/>
+        <v>-2.564102564102564E-2</v>
+      </c>
+      <c r="S6" s="112">
+        <f t="shared" si="0"/>
+        <v>-6.3291139240506333E-2</v>
+      </c>
+      <c r="T6" s="112">
+        <f t="shared" si="0"/>
+        <v>-4.9382716049382713E-2</v>
+      </c>
+      <c r="U6" s="112">
+        <f>(U5-Q5)/Q5</f>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="Z6" s="116"/>
+      <c r="AA6" s="112">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="112">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="2:30" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="110" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" s="110" t="s">
+        <v>328</v>
+      </c>
+      <c r="M7" s="110">
+        <v>61</v>
+      </c>
+      <c r="N7" s="110">
+        <v>118</v>
+      </c>
+      <c r="O7" s="110">
+        <v>106</v>
+      </c>
+      <c r="P7" s="110">
+        <v>62</v>
+      </c>
+      <c r="Q7" s="110">
+        <v>67</v>
+      </c>
+      <c r="R7" s="110">
+        <v>116</v>
+      </c>
+      <c r="S7" s="110">
+        <v>106</v>
+      </c>
+      <c r="T7" s="110">
+        <v>67</v>
+      </c>
+      <c r="U7" s="110">
+        <v>64</v>
+      </c>
+      <c r="Z7" s="115"/>
+    </row>
+    <row r="8" spans="2:30" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D8" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="112"/>
+      <c r="L8" s="112"/>
+      <c r="M8" s="112"/>
+      <c r="N8" s="112"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="112">
+        <f t="shared" ref="Q8:T8" si="1">(Q7-M7)/M7</f>
+        <v>9.8360655737704916E-2</v>
+      </c>
+      <c r="R8" s="112">
+        <f t="shared" si="1"/>
+        <v>-1.6949152542372881E-2</v>
+      </c>
+      <c r="S8" s="112">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="112">
+        <f t="shared" si="1"/>
+        <v>8.0645161290322578E-2</v>
+      </c>
+      <c r="U8" s="112">
+        <f>(U7-Q7)/Q7</f>
+        <v>-4.4776119402985072E-2</v>
+      </c>
+      <c r="V8" s="112"/>
+      <c r="W8" s="112"/>
+      <c r="X8" s="112"/>
+      <c r="Z8" s="117"/>
+      <c r="AA8" s="113">
+        <v>-0.06</v>
+      </c>
+      <c r="AB8" s="113">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="9" spans="2:30" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="110" t="s">
+        <v>327</v>
+      </c>
+      <c r="D9" s="110" t="s">
+        <v>326</v>
+      </c>
+      <c r="M9" s="110">
+        <v>251</v>
+      </c>
+      <c r="N9" s="110">
+        <v>255</v>
+      </c>
+      <c r="O9" s="110">
+        <v>242</v>
+      </c>
+      <c r="P9" s="110">
+        <v>240</v>
+      </c>
+      <c r="Q9" s="110">
+        <v>217</v>
+      </c>
+      <c r="R9" s="110">
+        <v>226</v>
+      </c>
+      <c r="S9" s="110">
+        <v>225</v>
+      </c>
+      <c r="T9" s="110">
+        <v>221</v>
+      </c>
+      <c r="U9" s="110">
+        <v>205</v>
+      </c>
+      <c r="Z9" s="115"/>
+    </row>
+    <row r="10" spans="2:30" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D10" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="112"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112"/>
+      <c r="P10" s="112"/>
+      <c r="Q10" s="112">
+        <f t="shared" ref="Q10:T10" si="2">(Q9-M9)/M9</f>
+        <v>-0.13545816733067728</v>
+      </c>
+      <c r="R10" s="112">
+        <f t="shared" si="2"/>
+        <v>-0.11372549019607843</v>
+      </c>
+      <c r="S10" s="112">
+        <f t="shared" si="2"/>
+        <v>-7.0247933884297523E-2</v>
+      </c>
+      <c r="T10" s="112">
+        <f t="shared" si="2"/>
+        <v>-7.9166666666666663E-2</v>
+      </c>
+      <c r="U10" s="112">
+        <f>(U9-Q9)/Q9</f>
+        <v>-5.5299539170506916E-2</v>
+      </c>
+      <c r="V10" s="112"/>
+      <c r="W10" s="112"/>
+      <c r="X10" s="112"/>
+      <c r="Z10" s="117"/>
+      <c r="AA10" s="113">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="AB10" s="113">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="110" t="s">
+        <v>327</v>
+      </c>
+      <c r="D11" s="110" t="s">
+        <v>328</v>
+      </c>
+      <c r="M11" s="110">
+        <v>165</v>
+      </c>
+      <c r="N11" s="110">
+        <v>265</v>
+      </c>
+      <c r="O11" s="110">
+        <v>181</v>
+      </c>
+      <c r="P11" s="110">
+        <v>107</v>
+      </c>
+      <c r="Q11" s="110">
+        <v>112</v>
+      </c>
+      <c r="R11" s="110">
+        <v>171</v>
+      </c>
+      <c r="S11" s="110">
+        <v>158</v>
+      </c>
+      <c r="T11" s="110">
+        <v>90</v>
+      </c>
+      <c r="U11" s="110">
+        <v>81</v>
+      </c>
+      <c r="Z11" s="115"/>
+    </row>
+    <row r="12" spans="2:30" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D12" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="112"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="112">
+        <f t="shared" ref="Q12:T12" si="3">(Q11-M11)/M11</f>
+        <v>-0.32121212121212123</v>
+      </c>
+      <c r="R12" s="112">
+        <f t="shared" si="3"/>
+        <v>-0.35471698113207545</v>
+      </c>
+      <c r="S12" s="112">
+        <f t="shared" si="3"/>
+        <v>-0.1270718232044199</v>
+      </c>
+      <c r="T12" s="112">
+        <f t="shared" si="3"/>
+        <v>-0.15887850467289719</v>
+      </c>
+      <c r="U12" s="112">
+        <f>(U11-Q11)/Q11</f>
+        <v>-0.2767857142857143</v>
+      </c>
+      <c r="V12" s="112"/>
+      <c r="W12" s="112"/>
+      <c r="X12" s="112"/>
+      <c r="Z12" s="117"/>
+      <c r="AA12" s="113">
+        <v>-0.35</v>
+      </c>
+      <c r="AB12" s="113">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="110" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="110" t="s">
+        <v>326</v>
+      </c>
+      <c r="M13" s="110">
+        <v>58</v>
+      </c>
+      <c r="N13" s="110">
+        <v>55</v>
+      </c>
+      <c r="O13" s="110">
+        <v>55</v>
+      </c>
+      <c r="P13" s="110">
+        <v>57</v>
+      </c>
+      <c r="Q13" s="110">
+        <v>53</v>
+      </c>
+      <c r="R13" s="110">
+        <v>52</v>
+      </c>
+      <c r="S13" s="110">
+        <v>51</v>
+      </c>
+      <c r="T13" s="110">
+        <v>53</v>
+      </c>
+      <c r="U13" s="110">
+        <v>65</v>
+      </c>
+      <c r="Z13" s="115"/>
+    </row>
+    <row r="14" spans="2:30" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D14" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="112"/>
+      <c r="F14" s="112"/>
+      <c r="G14" s="112"/>
+      <c r="H14" s="112"/>
+      <c r="I14" s="112"/>
+      <c r="J14" s="112"/>
+      <c r="K14" s="112"/>
+      <c r="L14" s="112"/>
+      <c r="M14" s="112"/>
+      <c r="N14" s="112"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="112">
+        <f t="shared" ref="Q14:T14" si="4">(Q13-M13)/M13</f>
+        <v>-8.6206896551724144E-2</v>
+      </c>
+      <c r="R14" s="112">
+        <f t="shared" si="4"/>
+        <v>-5.4545454545454543E-2</v>
+      </c>
+      <c r="S14" s="112">
+        <f t="shared" si="4"/>
+        <v>-7.2727272727272724E-2</v>
+      </c>
+      <c r="T14" s="112">
+        <f t="shared" si="4"/>
+        <v>-7.0175438596491224E-2</v>
+      </c>
+      <c r="U14" s="112">
+        <f>(U13-Q13)/Q13</f>
+        <v>0.22641509433962265</v>
+      </c>
+      <c r="V14" s="112"/>
+      <c r="W14" s="112"/>
+      <c r="X14" s="112"/>
+      <c r="Z14" s="117"/>
+    </row>
+    <row r="15" spans="2:30" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="110" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" s="110" t="s">
+        <v>328</v>
+      </c>
+      <c r="M15" s="110">
+        <v>51</v>
+      </c>
+      <c r="N15" s="110">
+        <v>62</v>
+      </c>
+      <c r="O15" s="110">
+        <v>58</v>
+      </c>
+      <c r="P15" s="110">
+        <v>45</v>
+      </c>
+      <c r="Q15" s="110">
+        <v>36</v>
+      </c>
+      <c r="R15" s="110">
+        <v>30</v>
+      </c>
+      <c r="S15" s="110">
+        <v>28</v>
+      </c>
+      <c r="T15" s="110">
+        <v>27</v>
+      </c>
+      <c r="U15" s="110">
+        <v>27</v>
+      </c>
+      <c r="Z15" s="115"/>
+    </row>
+    <row r="16" spans="2:30" s="113" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="D16" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" s="112"/>
+      <c r="F16" s="112"/>
+      <c r="G16" s="112"/>
+      <c r="H16" s="112"/>
+      <c r="I16" s="112"/>
+      <c r="J16" s="112"/>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112"/>
+      <c r="M16" s="112"/>
+      <c r="N16" s="112"/>
+      <c r="O16" s="112"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="112">
+        <f t="shared" ref="Q16:T16" si="5">(Q15-M15)/M15</f>
+        <v>-0.29411764705882354</v>
+      </c>
+      <c r="R16" s="112">
+        <f t="shared" si="5"/>
+        <v>-0.5161290322580645</v>
+      </c>
+      <c r="S16" s="112">
+        <f t="shared" si="5"/>
+        <v>-0.51724137931034486</v>
+      </c>
+      <c r="T16" s="112">
+        <f t="shared" si="5"/>
+        <v>-0.4</v>
+      </c>
+      <c r="U16" s="112">
+        <f>(U15-Q15)/Q15</f>
+        <v>-0.25</v>
+      </c>
+      <c r="V16" s="112"/>
+      <c r="W16" s="112"/>
+      <c r="X16" s="112"/>
+      <c r="Z16" s="117"/>
+      <c r="AA16" s="113">
+        <v>-0.37</v>
+      </c>
+      <c r="AB16" s="113">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z17" s="118"/>
+    </row>
+    <row r="18" spans="2:28" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="109" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" s="110" t="s">
+        <v>325</v>
+      </c>
+      <c r="D18" s="110" t="s">
+        <v>331</v>
+      </c>
+      <c r="M18" s="110">
+        <v>51</v>
+      </c>
+      <c r="N18" s="110">
+        <v>74</v>
+      </c>
+      <c r="O18" s="110">
+        <v>67</v>
+      </c>
+      <c r="P18" s="110">
+        <v>49</v>
+      </c>
+      <c r="Q18" s="110">
+        <v>55</v>
+      </c>
+      <c r="R18" s="110">
+        <v>70</v>
+      </c>
+      <c r="S18" s="110">
+        <v>61</v>
+      </c>
+      <c r="T18" s="110">
+        <v>45</v>
+      </c>
+      <c r="U18" s="110">
+        <v>52</v>
+      </c>
+      <c r="Z18" s="115"/>
+    </row>
+    <row r="19" spans="2:28" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="114"/>
+      <c r="D19" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="112"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="112"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="112">
+        <f t="shared" ref="Q19:T19" si="6">(Q18-M18)/M18</f>
+        <v>7.8431372549019607E-2</v>
+      </c>
+      <c r="R19" s="112">
+        <f t="shared" si="6"/>
+        <v>-5.4054054054054057E-2</v>
+      </c>
+      <c r="S19" s="112">
+        <f t="shared" si="6"/>
+        <v>-8.9552238805970144E-2</v>
+      </c>
+      <c r="T19" s="112">
+        <f t="shared" si="6"/>
+        <v>-8.1632653061224483E-2</v>
+      </c>
+      <c r="U19" s="112">
+        <f>(U18-Q18)/Q18</f>
+        <v>-5.4545454545454543E-2</v>
+      </c>
+      <c r="Z19" s="119"/>
+      <c r="AA19" s="44">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="44">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="110" t="s">
+        <v>325</v>
+      </c>
+      <c r="D20" s="110" t="s">
+        <v>332</v>
+      </c>
+      <c r="M20" s="110">
+        <v>23</v>
+      </c>
+      <c r="N20" s="110">
+        <v>38</v>
+      </c>
+      <c r="O20" s="110">
+        <v>31</v>
+      </c>
+      <c r="P20" s="110">
+        <v>21</v>
+      </c>
+      <c r="Q20" s="110">
+        <v>29</v>
+      </c>
+      <c r="R20" s="110">
+        <v>40</v>
+      </c>
+      <c r="S20" s="110">
+        <v>30</v>
+      </c>
+      <c r="T20" s="110">
+        <v>21</v>
+      </c>
+      <c r="U20" s="110">
+        <v>27</v>
+      </c>
+      <c r="Z20" s="115"/>
+    </row>
+    <row r="21" spans="2:28" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="112"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="112"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112">
+        <f t="shared" ref="Q21:T21" si="7">(Q20-M20)/M20</f>
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="R21" s="112">
+        <f t="shared" si="7"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="S21" s="112">
+        <f t="shared" si="7"/>
+        <v>-3.2258064516129031E-2</v>
+      </c>
+      <c r="T21" s="112">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="112">
+        <f>(U20-Q20)/Q20</f>
+        <v>-6.8965517241379309E-2</v>
+      </c>
+      <c r="Z21" s="119"/>
+      <c r="AA21" s="44">
+        <v>0.05</v>
+      </c>
+      <c r="AB21" s="44">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="M22" s="14">
+        <v>104</v>
+      </c>
+      <c r="N22" s="14">
+        <v>111</v>
+      </c>
+      <c r="O22" s="14">
+        <v>107</v>
+      </c>
+      <c r="P22" s="14">
+        <v>91</v>
+      </c>
+      <c r="Q22" s="14">
+        <v>103</v>
+      </c>
+      <c r="R22" s="14">
+        <v>108</v>
+      </c>
+      <c r="S22" s="14">
+        <v>97</v>
+      </c>
+      <c r="T22" s="14">
+        <v>88</v>
+      </c>
+      <c r="U22" s="14">
+        <v>1569</v>
+      </c>
+      <c r="Z22" s="10"/>
+    </row>
+    <row r="23" spans="2:28" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="112"/>
+      <c r="F23" s="112"/>
+      <c r="G23" s="112"/>
+      <c r="H23" s="112"/>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="112">
+        <f t="shared" ref="Q23:T23" si="8">(Q22-M22)/M22</f>
+        <v>-9.6153846153846159E-3</v>
+      </c>
+      <c r="R23" s="112">
+        <f t="shared" si="8"/>
+        <v>-2.7027027027027029E-2</v>
+      </c>
+      <c r="S23" s="112">
+        <f t="shared" si="8"/>
+        <v>-9.3457943925233641E-2</v>
+      </c>
+      <c r="T23" s="112">
+        <f t="shared" si="8"/>
+        <v>-3.2967032967032968E-2</v>
+      </c>
+      <c r="U23" s="112">
+        <f>(U22-Q22)/Q22</f>
+        <v>14.233009708737864</v>
+      </c>
+      <c r="Z23" s="119"/>
+    </row>
+    <row r="24" spans="2:28" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z24" s="118"/>
+    </row>
+    <row r="25" spans="2:28" s="110" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="109" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="110" t="s">
+        <v>325</v>
+      </c>
+      <c r="D25" s="110" t="s">
+        <v>331</v>
+      </c>
+      <c r="M25" s="110">
+        <v>44</v>
+      </c>
+      <c r="N25" s="110">
+        <v>41</v>
+      </c>
+      <c r="O25" s="110">
+        <v>35</v>
+      </c>
+      <c r="P25" s="110">
+        <v>34</v>
+      </c>
+      <c r="Q25" s="110">
+        <v>40</v>
+      </c>
+      <c r="R25" s="110">
+        <v>35</v>
+      </c>
+      <c r="S25" s="110">
+        <v>30</v>
+      </c>
+      <c r="T25" s="110">
+        <v>31</v>
+      </c>
+      <c r="U25" s="110">
+        <v>38</v>
+      </c>
+      <c r="Z25" s="115"/>
+    </row>
+    <row r="26" spans="2:28" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
+      <c r="M26" s="112"/>
+      <c r="N26" s="112"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="112"/>
+      <c r="Q26" s="112">
+        <f t="shared" ref="Q26:T26" si="9">(Q25-M25)/M25</f>
+        <v>-9.0909090909090912E-2</v>
+      </c>
+      <c r="R26" s="112">
+        <f t="shared" si="9"/>
+        <v>-0.14634146341463414</v>
+      </c>
+      <c r="S26" s="112">
+        <f t="shared" si="9"/>
+        <v>-0.14285714285714285</v>
+      </c>
+      <c r="T26" s="112">
+        <f t="shared" si="9"/>
+        <v>-8.8235294117647065E-2</v>
+      </c>
+      <c r="U26" s="112">
+        <f>(U25-Q25)/Q25</f>
+        <v>-0.05</v>
+      </c>
+      <c r="Z26" s="119"/>
+      <c r="AA26" s="44">
+        <v>-0.08</v>
+      </c>
+      <c r="AB26" s="44">
+        <v>-0.13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D917182-8725-1A42-930E-2FA6BEC1ABF8}">
+  <dimension ref="A2:AC18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
+    <col min="21" max="21" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.83203125" style="125"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="Z4" s="125" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="19" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q5" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="S5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="T5" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="U5" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="V5" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="Z5" s="126" t="s">
+        <v>336</v>
+      </c>
+      <c r="AA5" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="AB5" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="AC5" s="13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" s="105" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="B6" s="104" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="105" t="s">
+        <v>325</v>
+      </c>
+      <c r="D6" s="105" t="s">
+        <v>342</v>
+      </c>
+      <c r="O6" s="105">
+        <v>481</v>
+      </c>
+      <c r="P6" s="105">
+        <v>540</v>
+      </c>
+      <c r="Q6" s="105">
+        <v>531</v>
+      </c>
+      <c r="R6" s="105">
+        <v>549</v>
+      </c>
+      <c r="S6" s="105">
+        <v>569</v>
+      </c>
+      <c r="T6" s="105">
+        <v>620</v>
+      </c>
+      <c r="U6" s="105">
+        <v>634</v>
+      </c>
+      <c r="Z6" s="127"/>
+    </row>
+    <row r="7" spans="1:29" s="124" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="111"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="S7" s="124">
+        <f>(S6-O6)/O6</f>
+        <v>0.18295218295218296</v>
+      </c>
+      <c r="T7" s="124">
+        <f>(T6-P6)/P6</f>
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="U7" s="124">
+        <f>(U6-Q6)/Q6</f>
+        <v>0.19397363465160075</v>
+      </c>
+      <c r="Z7" s="128">
+        <v>0.19</v>
+      </c>
+      <c r="AA7" s="124">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" s="44" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="C8" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="O8" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="P8" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="Q8" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="R8" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="S8" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="T8" s="44">
+        <v>0.17</v>
+      </c>
+      <c r="U8" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="Z8" s="129"/>
+    </row>
+    <row r="9" spans="1:29" s="122" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="B9" s="106"/>
+      <c r="C9" s="106" t="s">
+        <v>327</v>
+      </c>
+      <c r="D9" s="106" t="s">
+        <v>342</v>
+      </c>
+      <c r="O9" s="122">
+        <v>173</v>
+      </c>
+      <c r="P9" s="122">
+        <v>177</v>
+      </c>
+      <c r="Q9" s="122">
+        <v>201</v>
+      </c>
+      <c r="R9" s="122">
+        <v>191</v>
+      </c>
+      <c r="S9" s="122">
+        <v>198</v>
+      </c>
+      <c r="T9" s="122">
+        <v>176</v>
+      </c>
+      <c r="U9" s="122">
+        <v>180</v>
+      </c>
+      <c r="Z9" s="130"/>
+    </row>
+    <row r="10" spans="1:29" s="124" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="S10" s="124">
+        <f>(S9-O9)/O9</f>
+        <v>0.14450867052023122</v>
+      </c>
+      <c r="T10" s="124">
+        <f>(T9-P9)/P9</f>
+        <v>-5.6497175141242938E-3</v>
+      </c>
+      <c r="U10" s="124">
+        <f>(U9-Q9)/Q9</f>
+        <v>-0.1044776119402985</v>
+      </c>
+      <c r="Z10" s="128">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="AA10" s="124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" s="44" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="C11" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="O11" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="P11" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="Q11" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="R11" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="S11" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="T11" s="44">
+        <v>0.11</v>
+      </c>
+      <c r="U11" s="44">
+        <v>0.11</v>
+      </c>
+      <c r="Z11" s="129"/>
+    </row>
+    <row r="12" spans="1:29" s="123" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="B12" s="108"/>
+      <c r="C12" s="108" t="s">
+        <v>333</v>
+      </c>
+      <c r="D12" s="108" t="s">
+        <v>342</v>
+      </c>
+      <c r="O12" s="123">
+        <v>8</v>
+      </c>
+      <c r="P12" s="123">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="123">
+        <v>12</v>
+      </c>
+      <c r="R12" s="123">
+        <v>13</v>
+      </c>
+      <c r="S12" s="123">
+        <v>16</v>
+      </c>
+      <c r="T12" s="123">
+        <v>18</v>
+      </c>
+      <c r="U12" s="123">
+        <v>17</v>
+      </c>
+      <c r="Z12" s="131"/>
+    </row>
+    <row r="13" spans="1:29" s="124" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="S13" s="124">
+        <f>(S12-O12)/O12</f>
+        <v>1</v>
+      </c>
+      <c r="T13" s="124">
+        <f>(T12-P12)/P12</f>
+        <v>0.5</v>
+      </c>
+      <c r="U13" s="124">
+        <f>(U12-Q12)/Q12</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="Z13" s="128">
+        <v>0.46</v>
+      </c>
+      <c r="AA13" s="124">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" s="44" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="C14" s="44" t="s">
+        <v>333</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="O14" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="P14" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="Q14" s="44">
+        <v>0.17</v>
+      </c>
+      <c r="R14" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="S14" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="T14" s="44">
+        <v>0.17</v>
+      </c>
+      <c r="U14" s="44">
+        <v>0.17</v>
+      </c>
+      <c r="Z14" s="129"/>
+    </row>
+    <row r="15" spans="1:29" s="107" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="C15" s="107" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" s="107" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q15" s="107">
+        <v>16</v>
+      </c>
+      <c r="R15" s="107">
+        <v>33</v>
+      </c>
+      <c r="S15" s="107">
+        <v>40</v>
+      </c>
+      <c r="T15" s="107">
+        <v>51</v>
+      </c>
+      <c r="U15" s="107">
+        <v>57</v>
+      </c>
+      <c r="Z15" s="132"/>
+    </row>
+    <row r="16" spans="1:29" s="124" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D16" s="124" t="s">
+        <v>171</v>
+      </c>
+      <c r="U16" s="124">
+        <f>(U15-Q15)/Q15</f>
+        <v>2.5625</v>
+      </c>
+      <c r="Z16" s="128"/>
+      <c r="AA16" s="124">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="17" spans="3:26" s="44" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="C17" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q17" s="44">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="R17" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="S17" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="T17" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="U17" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="Z17" s="129"/>
+    </row>
+    <row r="18" spans="3:26" s="121" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="Z18" s="133"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67A06AA-8C1B-0A45-89DE-B4BD1A467A96}">
   <dimension ref="C4:F7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -19930,15 +22452,15 @@
       </c>
       <c r="D5" s="42">
         <f>Modell!$B$9/Modell!AG17</f>
-        <v>20.065072931314969</v>
+        <v>18.806549834757295</v>
       </c>
       <c r="E5" s="65">
         <f>Modell!$B$9/Modell!AH17</f>
-        <v>15.775192208046171</v>
+        <v>14.785739350614586</v>
       </c>
       <c r="F5" s="68">
         <f>Modell!$B$9/Modell!AI17</f>
-        <v>12.789704992034745</v>
+        <v>11.987508100663673</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -19947,15 +22469,15 @@
       </c>
       <c r="D6" s="42">
         <f>Modell!$B$9/Modell!AG22</f>
-        <v>31.085196101764215</v>
+        <v>29.135467965264937</v>
       </c>
       <c r="E6" s="65">
         <f>Modell!$B$9/Modell!AH22</f>
-        <v>21.871080366983556</v>
+        <v>20.499280728739532</v>
       </c>
       <c r="F6" s="68">
         <f>Modell!$B$9/Modell!AI22</f>
-        <v>16.969412947991007</v>
+        <v>15.905056082547411</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
@@ -19964,15 +22486,15 @@
       </c>
       <c r="D7" s="42">
         <f>Modell!$B$4/Modell!AG31</f>
-        <v>41.376859658535878</v>
+        <v>38.942926737445532</v>
       </c>
       <c r="E7" s="65">
         <f>Modell!$B$4/Modell!AH31</f>
-        <v>29.112141353802748</v>
+        <v>27.39966245063788</v>
       </c>
       <c r="F7" s="67">
         <f>Modell!$B$4/Modell!AI31</f>
-        <v>22.587633539069614</v>
+        <v>21.258949213241991</v>
       </c>
     </row>
   </sheetData>
@@ -19980,7 +22502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81175711-CD5D-F541-B2D0-1F8283D6638C}">
   <dimension ref="A1:EO41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -20099,7 +22621,7 @@
       </c>
       <c r="B6" s="70">
         <f>Modell!B9</f>
-        <v>50939</v>
+        <v>47744</v>
       </c>
       <c r="C6"/>
       <c r="D6"/>
@@ -20185,7 +22707,7 @@
       </c>
       <c r="D9" s="98">
         <f>B9/$B$6-1</f>
-        <v>-0.36609330218496616</v>
+        <v>-0.32367264410187646</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -20217,7 +22739,7 @@
       </c>
       <c r="D10" s="99">
         <f t="shared" ref="D10:D29" si="1">B10/$B$6-1</f>
-        <v>-0.30270263240346285</v>
+        <v>-0.25603990851206415</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -20249,7 +22771,7 @@
       </c>
       <c r="D11" s="99">
         <f t="shared" si="1"/>
-        <v>-0.23931196262195942</v>
+        <v>-0.18840717292225184</v>
       </c>
       <c r="E11"/>
       <c r="F11"/>
@@ -20281,7 +22803,7 @@
       </c>
       <c r="D12" s="99">
         <f t="shared" si="1"/>
-        <v>-0.17592129284045599</v>
+        <v>-0.12077443733243942</v>
       </c>
       <c r="E12"/>
       <c r="F12"/>
@@ -20313,7 +22835,7 @@
       </c>
       <c r="D13" s="99">
         <f t="shared" si="1"/>
-        <v>-0.11253062305895267</v>
+        <v>-5.3141701742627223E-2</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -20345,7 +22867,7 @@
       </c>
       <c r="D14" s="99">
         <f t="shared" si="1"/>
-        <v>-4.9139953277449355E-2</v>
+        <v>1.4491033847185086E-2</v>
       </c>
       <c r="E14"/>
       <c r="F14"/>
@@ -20377,7 +22899,7 @@
       </c>
       <c r="D15" s="99">
         <f t="shared" si="1"/>
-        <v>1.4250716504054184E-2</v>
+        <v>8.2123769436997618E-2</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -20409,7 +22931,7 @@
       </c>
       <c r="D16" s="99">
         <f t="shared" si="1"/>
-        <v>7.7641386285557612E-2</v>
+        <v>0.14975650502680993</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -20441,7 +22963,7 @@
       </c>
       <c r="D17" s="99">
         <f t="shared" si="1"/>
-        <v>0.14103205606706104</v>
+        <v>0.21738924061662246</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -20473,7 +22995,7 @@
       </c>
       <c r="D18" s="99">
         <f t="shared" si="1"/>
-        <v>0.20442272584856425</v>
+        <v>0.28502197620643455</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -20505,7 +23027,7 @@
       </c>
       <c r="D19" s="100">
         <f t="shared" si="1"/>
-        <v>0.26781339563006767</v>
+        <v>0.35265471179624708</v>
       </c>
       <c r="E19"/>
       <c r="F19"/>
@@ -20537,7 +23059,7 @@
       </c>
       <c r="D20" s="99">
         <f t="shared" si="1"/>
-        <v>0.3312040654115711</v>
+        <v>0.42028744738605939</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -20569,7 +23091,7 @@
       </c>
       <c r="D21" s="99">
         <f t="shared" si="1"/>
-        <v>0.39459473519307431</v>
+        <v>0.4879201829758717</v>
       </c>
       <c r="E21"/>
       <c r="F21"/>
@@ -20601,7 +23123,7 @@
       </c>
       <c r="D22" s="99">
         <f t="shared" si="1"/>
-        <v>0.45798540497457796</v>
+        <v>0.55555291856568423</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
@@ -20633,7 +23155,7 @@
       </c>
       <c r="D23" s="99">
         <f t="shared" si="1"/>
-        <v>0.52137607475608116</v>
+        <v>0.62318565415549632</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
@@ -20665,7 +23187,7 @@
       </c>
       <c r="D24" s="99">
         <f t="shared" si="1"/>
-        <v>0.58476674453758437</v>
+        <v>0.69081838974530863</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
@@ -20697,7 +23219,7 @@
       </c>
       <c r="D25" s="99">
         <f t="shared" si="1"/>
-        <v>0.64815741431908802</v>
+        <v>0.75845112533512116</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
@@ -20729,7 +23251,7 @@
       </c>
       <c r="D26" s="99">
         <f t="shared" si="1"/>
-        <v>0.71154808410059123</v>
+        <v>0.82608386092493347</v>
       </c>
       <c r="E26"/>
       <c r="F26"/>
@@ -20761,7 +23283,7 @@
       </c>
       <c r="D27" s="99">
         <f t="shared" si="1"/>
-        <v>0.77493875388209466</v>
+        <v>0.89371659651474555</v>
       </c>
       <c r="E27"/>
       <c r="F27"/>
@@ -20793,7 +23315,7 @@
       </c>
       <c r="D28" s="99">
         <f t="shared" si="1"/>
-        <v>0.83832942366359808</v>
+        <v>0.96134933210455809</v>
       </c>
       <c r="E28"/>
       <c r="F28"/>
@@ -20825,7 +23347,7 @@
       </c>
       <c r="D29" s="101">
         <f t="shared" si="1"/>
-        <v>0.90172009344510129</v>
+        <v>1.0289820676943702</v>
       </c>
       <c r="E29"/>
       <c r="F29"/>
